--- a/MenuGen_Backlog.xlsx
+++ b/MenuGen_Backlog.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="13">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -101,12 +101,8 @@
       <family val="0"/>
       <sz val="11"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00006100"/>
-    </font>
   </fonts>
-  <fills count="12">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -167,12 +163,6 @@
         <bgColor rgb="FFD6E4F0"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB99"/>
-        <bgColor rgb="FFFFEB99"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -208,7 +198,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -344,18 +334,6 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -1177,12 +1155,12 @@
       </c>
       <c r="E9" s="28" t="inlineStr">
         <is>
-          <t>✅ (web) Профиль семьи: показ БЖУ и выбор meal_plan</t>
+          <t>Профиль семьи: показ БЖУ и выбор meal_plan</t>
         </is>
       </c>
       <c r="F9" s="28" t="inlineStr">
         <is>
-          <t>В форме редактирования участника семьи показывать рассчитанные protein/fat/carb_target_g (read-only, помечать «рассчитано автоматически») и добавить выбор meal_plan_type. [MG-204 web сделано — типы FamilyMember расширены, FamilyMemberEditModal, DayNutritionSummary в MenuPage. Mobile отложен.]</t>
+          <t>В форме редактирования участника семьи показывать рассчитанные protein/fat/carb_target_g (read-only, помечать «рассчитано автоматически») и добавить выбор meal_plan_type.</t>
         </is>
       </c>
       <c r="G9" s="28" t="inlineStr">
@@ -1228,9 +1206,9 @@
           <t>Спринт 2</t>
         </is>
       </c>
-      <c r="E10" s="46" t="inlineStr">
-        <is>
-          <t>✅ Отслеживание источника правок КБЖУ (auto / user / specialist)</t>
+      <c r="E10" s="32" t="inlineStr">
+        <is>
+          <t>Отслеживание источника правок КБЖУ (auto / user / specialist)</t>
         </is>
       </c>
       <c r="F10" s="32" t="inlineStr">
@@ -1971,53 +1949,14 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="47" t="inlineStr">
-        <is>
-          <t>MG-205-UI</t>
-        </is>
-      </c>
-      <c r="B24" s="47" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C24" s="47" t="inlineStr">
-        <is>
-          <t>Backend / Logic</t>
-        </is>
-      </c>
-      <c r="D24" s="47" t="inlineStr">
-        <is>
-          <t>Спринт 2</t>
-        </is>
-      </c>
-      <c r="E24" s="47" t="inlineStr">
-        <is>
-          <t>UI: бейджи источника правок КБЖУ + кнопка 'Сбросить к авто' + история</t>
-        </is>
-      </c>
-      <c r="F24" s="47" t="inlineStr">
-        <is>
-          <t>На фронте (React) и в мобайле (Flutter) для каждого поля КБЖУ (calorie/protein/fat/carb/fiber_target_g) показывать бейдж источника: «авто» / «вручную» / «диетолог N». Кнопка «Сбросить к авто» рядом — вызывает API force-сброса. По клику на бейдж — модалка с историей правок (ProfileTargetAudit), показывающая time/source/by_user/value.</t>
-        </is>
-      </c>
-      <c r="G24" s="47" t="inlineStr">
-        <is>
-          <t>web/menugen-web/src/pages/Profile/ProfilePage.tsx, web/menugen-web/src/types/index.ts, mobile/menugen_app/lib/screens/profile/, backend: новый endpoint POST /api/v1/users/me/targets/{field}/reset, backend: GET /api/v1/users/me/targets/{field}/history</t>
-        </is>
-      </c>
-      <c r="H24" s="47" t="inlineStr">
-        <is>
-          <t>Реализовать UI поверх данных MG-205. Backend: добавить два endpoint'а — GET history (список ProfileTargetAudit по полю) и POST reset (вызывает fill_profile_targets(force=True, actor=request.user) только для одного поля). На фронте: компонент &lt;TargetField/&gt; с бейджем и dropdown'ом-историей. Аналогично в Flutter. Тесты: API + UI snapshot. Зависит от: MG-205 (✅) и MG-204.</t>
-        </is>
-      </c>
-      <c r="I24" s="48" t="inlineStr">
-        <is>
-          <t>MG-205, MG-204</t>
-        </is>
-      </c>
-      <c r="J24" s="49" t="n">
-        <v>4</v>
+      <c r="I24" s="34" t="inlineStr">
+        <is>
+          <t>ИТОГО:</t>
+        </is>
+      </c>
+      <c r="J24" s="35">
+        <f>SUM(J2:J22)</f>
+        <v/>
       </c>
     </row>
   </sheetData>

--- a/MenuGen_Backlog.xlsx
+++ b/MenuGen_Backlog.xlsx
@@ -438,7 +438,26 @@
     <t xml:space="preserve">Спринт 4</t>
   </si>
   <si>
-    <t xml:space="preserve">Отображение меню по компонентам</t>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve">✅</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Отображение меню по компонентам</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">В MenuPage показывать приём пищи как карточку с 3 компонентами (зерновые / белки / овощи). У каждого свой рецепт со своей кнопкой замены.</t>
@@ -455,7 +474,26 @@
     <t xml:space="preserve">MG-402</t>
   </si>
   <si>
-    <t xml:space="preserve">Замена рецепта — фильтрация по component_role</t>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve">✅</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Замена рецепта — фильтрация по component_role</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">При замене рецепта в меню показывать только рецепты с тем же food_group, что и заменяемый.</t>
@@ -472,7 +510,26 @@
     <t xml:space="preserve">MG-403</t>
   </si>
   <si>
-    <t xml:space="preserve">Сводка КБЖУ за день</t>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve">✅</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Сводка КБЖУ за день</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">В MenuPage над каждым днём показывать суммарные КБЖУ всех приёмов и сравнение с целью пользователя (прогресс-бары).</t>
@@ -497,7 +554,26 @@
     <t xml:space="preserve">Спринт 5</t>
   </si>
   <si>
-    <t xml:space="preserve">Дополнительные поля Recipe: cooking_method, has_added_sugar, oil_tsp</t>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve">✅</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Дополнительные поля Recipe: cooking_method, has_added_sugar, oil_tsp</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">Поля для контроля метода готовки, добавленного сахара и расхода масла.</t>
@@ -519,7 +595,26 @@
     <t xml:space="preserve">MG-502</t>
   </si>
   <si>
-    <t xml:space="preserve">Контроль масла ≤5 ч.л./день в генераторе</t>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve">✅</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Контроль масла ≤5 ч.л./день в генераторе</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">Суммировать oil_tsp по всем рецептам дня; если &gt;5 — снижать вероятность выбора рецептов с oil_tsp&gt;1.</t>
@@ -531,7 +626,26 @@
     <t xml:space="preserve">MG-503</t>
   </si>
   <si>
-    <t xml:space="preserve">Исключение рецептов с добавленным сахаром из основных приёмов</t>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve">✅</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Исключение рецептов с добавленным сахаром из основных приёмов</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">В основные приёмы (breakfast/lunch/dinner) не подставлять рецепты с has_added_sugar=True. Разрешать только в snack (как сладость, 1 раз в день).</t>
@@ -1859,7 +1973,7 @@
       <c r="D15" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="E15" s="6" t="s">
+      <c r="E15" s="12" t="s">
         <v>89</v>
       </c>
       <c r="F15" s="6" t="s">
@@ -1891,7 +2005,7 @@
       <c r="D16" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="E16" s="6" t="s">
+      <c r="E16" s="12" t="s">
         <v>94</v>
       </c>
       <c r="F16" s="6" t="s">
@@ -1923,7 +2037,7 @@
       <c r="D17" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="E17" s="6" t="s">
+      <c r="E17" s="12" t="s">
         <v>99</v>
       </c>
       <c r="F17" s="6" t="s">
@@ -1955,7 +2069,7 @@
       <c r="D18" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="E18" s="6" t="s">
+      <c r="E18" s="12" t="s">
         <v>107</v>
       </c>
       <c r="F18" s="6" t="s">
@@ -1987,7 +2101,7 @@
       <c r="D19" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="E19" s="6" t="s">
+      <c r="E19" s="12" t="s">
         <v>112</v>
       </c>
       <c r="F19" s="6" t="s">
@@ -2019,7 +2133,7 @@
       <c r="D20" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="E20" s="6" t="s">
+      <c r="E20" s="12" t="s">
         <v>116</v>
       </c>
       <c r="F20" s="6" t="s">

--- a/MenuGen_Backlog.xlsx
+++ b/MenuGen_Backlog.xlsx
@@ -744,7 +744,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:J24"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="10" customWidth="1" style="27" min="1" max="1"/>
@@ -2055,6 +2055,56 @@
       </c>
       <c r="J24" s="43" t="n">
         <v>4</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>MG-T15</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Backend / Data</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>🟡 Наполнить БД рецептами для s1 (борьба с повторами)</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Высокая повторяемость рецептов в стратегии 1. Диагностика mg_analyze_s1_repeats показала: причина не в алгоритме, а в нехватке пула. Формула N≥d/T (min=1×d, good=4×d, great=10×d при d слотов/нед). Сделано: убраны напитки из s1 (MG_DRINK), импорт tati_cooks (MG_TGIMPORT, salad 20→32). Осталось дотянуть жёлтые пулы до good(4×спрос): salad 32→56, snack 26→56, bakery 27→28. Нужен ещё источник рецептов с КБЖУ.</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>backend/apps/menu/generator.py, backend/apps/menu/management/commands/mg_analyze_s1_repeats.py, backend/apps/recipes/management/commands/import_telegram_recipes.py</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Найти источник салатов/снеков с КБЖУ; написать парсер/импорт по образцу import_telegram_recipes; после импорта прогнать mg_seed_plate --apply, mg_backfill_recipe_products, mg_analyze_s1_repeats --runs 20 --days 7.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>MG-301, MG-302</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
